--- a/BROMappings/Mapping BRO GMN Events.xlsx
+++ b/BROMappings/Mapping BRO GMN Events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/Datamodels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/BronDatamodel/BROMappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D1D39F66-6325-4F89-AC9C-F2C7351B7FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91422C61-E055-467D-B254-B2D41A180A75}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{D1D39F66-6325-4F89-AC9C-F2C7351B7FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7EAC1D4-8873-4C1D-9682-D8FA2D188297}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>BROBrondocument</t>
   </si>
@@ -54,140 +54,144 @@
     <t>Correctie (verwijdering)</t>
   </si>
   <si>
+    <t>GMN_MeasuringPoint</t>
+  </si>
+  <si>
+    <t>GMN_TubeReference</t>
+  </si>
+  <si>
+    <t>GMN_MeasuringPointEndDate</t>
+  </si>
+  <si>
+    <t>GMN_Closure</t>
+  </si>
+  <si>
+    <t>Correctie (datumtijd)</t>
+  </si>
+  <si>
+    <t>moveRequest</t>
+  </si>
+  <si>
+    <t>Einde meetnet</t>
+  </si>
+  <si>
+    <t>Meetpunt toegevoegd</t>
+  </si>
+  <si>
+    <t>Meetpunt beëindigd</t>
+  </si>
+  <si>
+    <t>Aanvullen</t>
+  </si>
+  <si>
+    <t>Beëindigen</t>
+  </si>
+  <si>
+    <t>Corrigeren</t>
+  </si>
+  <si>
+    <t>meetpuntToevoegen</t>
+  </si>
+  <si>
+    <t>meetpuntBeeindigen</t>
+  </si>
+  <si>
+    <t>monitoringbuisVervangen</t>
+  </si>
+  <si>
+    <t>Correctie (invoeging)</t>
+  </si>
+  <si>
+    <t>insertRequest</t>
+  </si>
+  <si>
+    <t>GMN-Beeindiging</t>
+  </si>
+  <si>
+    <t>vervangverzoek</t>
+  </si>
+  <si>
+    <t>verplaatsverzoek</t>
+  </si>
+  <si>
+    <t>invoegverzoek</t>
+  </si>
+  <si>
+    <t>verwijderverzoek</t>
+  </si>
+  <si>
+    <t>'Meetpunt beëindigd' kan niet gecorrigeerd worden, gebruik daarvoor move</t>
+  </si>
+  <si>
+    <t>Meetpunt verplaatst</t>
+  </si>
+  <si>
+    <t>Het nieuwe en oude meetpunt dienen dezelfde stijghoogte te representeren. Zo niet, gebruik dan 'meetpunt beëindigd en toegevoegd' i.p.v. 'meetpunt verplaatst'</t>
+  </si>
+  <si>
+    <t>Buis vervangen</t>
+  </si>
+  <si>
+    <t>Buis bijgeplaatst</t>
+  </si>
+  <si>
+    <t>Indien een buis van een put wordt vervangen, dan leidt dit noodgedwongen tot registratie van een nieuwe put in de BRO (en dus afsplitsing van de bestaande), terwijl er in werkelijkheid verder niets verandert. Met behulp van deze brongebeurtenis wordt de administratie navenant bijgewerkt, de oude en nieuwe buis houden daarbij dezelfde MeetpuntCode.</t>
+  </si>
+  <si>
+    <t>Indien een buis bij een put wordt bijgeplaatst, dan leidt dit noodgedwongen tot registratie van een nieuwe put in de BRO (en dus afsplitsing van de bestaande), terwijl er in werkelijkheid verder niets verandert. Met behulp van deze brongebeurtenis wordt de administratie navenant bijgewerkt, de oude en nieuwe buis houden daarbij dezelfde MeetpuntCode.</t>
+  </si>
+  <si>
+    <t>BRO_DO</t>
+  </si>
+  <si>
+    <t>Verwijderen</t>
+  </si>
+  <si>
+    <t>Object-UitRegistratie</t>
+  </si>
+  <si>
+    <t>Uit registratie</t>
+  </si>
+  <si>
+    <t>BRO_Servicedesk</t>
+  </si>
+  <si>
+    <t>leverancierVeranderd</t>
+  </si>
+  <si>
+    <t>Geen bericht of brondocument, maar actie BRO-servicedesk op verzoek</t>
+  </si>
+  <si>
+    <t>[Categorical]</t>
+  </si>
+  <si>
+    <t>[String]</t>
+  </si>
+  <si>
+    <t>BronOmschrijving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starten  </t>
+  </si>
+  <si>
+    <t>Start registratie</t>
+  </si>
+  <si>
     <t>GMN_StartRegistration </t>
   </si>
   <si>
-    <t>GMN_MeasuringPoint</t>
-  </si>
-  <si>
-    <t>GMN_TubeReference</t>
-  </si>
-  <si>
-    <t>GMN_MeasuringPointEndDate</t>
-  </si>
-  <si>
-    <t>GMN_Closure</t>
-  </si>
-  <si>
-    <t>Correctie (datumtijd)</t>
-  </si>
-  <si>
-    <t>moveRequest</t>
-  </si>
-  <si>
-    <t>Einde meetnet</t>
-  </si>
-  <si>
-    <t>Meetpunt toegevoegd</t>
-  </si>
-  <si>
-    <t>Meetpunt beëindigd</t>
-  </si>
-  <si>
-    <t>Start meetnet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starten  </t>
-  </si>
-  <si>
-    <t>Aanvullen</t>
-  </si>
-  <si>
-    <t>Beëindigen</t>
-  </si>
-  <si>
-    <t>Corrigeren</t>
-  </si>
-  <si>
-    <t>meetpuntToevoegen</t>
-  </si>
-  <si>
-    <t>meetpuntBeeindigen</t>
-  </si>
-  <si>
-    <t>monitoringbuisVervangen</t>
-  </si>
-  <si>
-    <t>Correctie (invoeging)</t>
-  </si>
-  <si>
-    <t>insertRequest</t>
-  </si>
-  <si>
-    <t>GMN-Beeindiging</t>
-  </si>
-  <si>
     <t>GMN-StartRegistratie</t>
   </si>
   <si>
-    <t>vervangverzoek</t>
-  </si>
-  <si>
-    <t>verplaatsverzoek</t>
-  </si>
-  <si>
-    <t>invoegverzoek</t>
-  </si>
-  <si>
-    <t>verwijderverzoek</t>
-  </si>
-  <si>
-    <t>'Meetpunt beëindigd' kan niet gecorrigeerd worden, gebruik daarvoor move</t>
-  </si>
-  <si>
-    <t>Meetpunt verplaatst</t>
-  </si>
-  <si>
-    <t>Het nieuwe en oude meetpunt dienen dezelfde stijghoogte te representeren. Zo niet, gebruik dan 'meetpunt beëindigd en toegevoegd' i.p.v. 'meetpunt verplaatst'</t>
-  </si>
-  <si>
-    <t>Buis vervangen</t>
-  </si>
-  <si>
-    <t>Buis bijgeplaatst</t>
-  </si>
-  <si>
-    <t>Indien een buis van een put wordt vervangen, dan leidt dit noodgedwongen tot registratie van een nieuwe put in de BRO (en dus afsplitsing van de bestaande), terwijl er in werkelijkheid verder niets verandert. Met behulp van deze brongebeurtenis wordt de administratie navenant bijgewerkt, de oude en nieuwe buis houden daarbij dezelfde MeetpuntCode.</t>
-  </si>
-  <si>
-    <t>Indien een buis bij een put wordt bijgeplaatst, dan leidt dit noodgedwongen tot registratie van een nieuwe put in de BRO (en dus afsplitsing van de bestaande), terwijl er in werkelijkheid verder niets verandert. Met behulp van deze brongebeurtenis wordt de administratie navenant bijgewerkt, de oude en nieuwe buis houden daarbij dezelfde MeetpuntCode.</t>
-  </si>
-  <si>
-    <t>BRO_DO</t>
-  </si>
-  <si>
-    <t>Verwijderen</t>
-  </si>
-  <si>
-    <t>Object-UitRegistratie</t>
-  </si>
-  <si>
-    <t>Uit registratie</t>
-  </si>
-  <si>
-    <t>BRO_Servicedesk</t>
-  </si>
-  <si>
-    <t>leverancierVeranderd</t>
-  </si>
-  <si>
-    <t>Geen bericht of brondocument, maar actie BRO-servicedesk op verzoek</t>
+    <t>De bijbehorende datum is de ObjRgstrDateTime in gmn.Adm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -200,16 +204,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF005E6A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85C9EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -218,19 +248,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -283,13 +300,13 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -298,43 +315,59 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -344,33 +377,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,248 +696,281 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.5703125" customWidth="1"/>
+    <col min="6" max="6" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="11" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="13"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
       <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="C11" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="D11" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="F11" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="10" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="C15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
